--- a/data/agg.data.xlsx
+++ b/data/agg.data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexg\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexg\Downloads\Pitt-ML-MSE-Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{711B0DC9-ED52-4544-849C-BCD0892323FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D311D528-553B-42BD-9F6D-8C4F2FB3FD11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{CF02A2AE-FF0A-47A5-AC02-8F225392EBF1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{CF02A2AE-FF0A-47A5-AC02-8F225392EBF1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -388,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12609426-CDA6-42F6-AD91-E6F051E1B6DE}">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -413,383 +413,820 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="B2">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="C2">
-        <v>0.76</v>
+        <v>0.71</v>
       </c>
       <c r="D2">
-        <v>0.35</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="C3">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="D3">
-        <v>0.34</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="B4">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="C4">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="D4">
-        <v>0.34</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="B5">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="C5">
-        <v>0.9</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="D5">
-        <v>0.59</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="B6">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="C6">
-        <v>0.9</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="D6">
-        <v>0.61</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="B7">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="C7">
-        <v>0.9</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="D7">
-        <v>0.59</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="B8">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="C8">
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
       <c r="D8">
-        <v>0.38</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="B9">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="C9">
-        <v>0.88</v>
+        <v>0.81</v>
       </c>
       <c r="D9">
-        <v>0.36</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="B10">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="C10">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="D10">
-        <v>0.38</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="B11">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="C11">
-        <v>0.98</v>
+        <v>0.62</v>
       </c>
       <c r="D11">
-        <v>0.41</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="B12">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="C12">
-        <v>0.95</v>
+        <v>0.61</v>
       </c>
       <c r="D12">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="B13">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="C13">
-        <v>0.94</v>
+        <v>0.62</v>
       </c>
       <c r="D13">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>0.5</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="B14">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="C14">
-        <v>1.29</v>
+        <v>0.82</v>
       </c>
       <c r="D14">
-        <v>0.52</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>0.5</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="B15">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="C15">
-        <v>1.28</v>
+        <v>0.83</v>
       </c>
       <c r="D15">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>0.5</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="B16">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="C16">
-        <v>1.3</v>
+        <v>0.82</v>
       </c>
       <c r="D16">
-        <v>0.51</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="B17">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="C17">
-        <v>2.02</v>
+        <v>0.68</v>
       </c>
       <c r="D17">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="B18">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="C18">
-        <v>2.0099999999999998</v>
+        <v>0.68</v>
       </c>
       <c r="D18">
-        <v>0.59</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="B19">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="C19">
-        <v>2.0099999999999998</v>
+        <v>0.69</v>
       </c>
       <c r="D19">
-        <v>0.56999999999999995</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>2.5</v>
+        <v>0.09</v>
       </c>
       <c r="B20">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="C20">
-        <v>3.55</v>
+        <v>0.88</v>
       </c>
       <c r="D20">
-        <v>0.56999999999999995</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>2.5</v>
+        <v>0.09</v>
       </c>
       <c r="B21">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="C21">
-        <v>3.63</v>
+        <v>0.87</v>
       </c>
       <c r="D21">
-        <v>0.56999999999999995</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>2.5</v>
+        <v>0.09</v>
       </c>
       <c r="B22">
         <v>1.44</v>
       </c>
       <c r="C22">
-        <v>3.61</v>
+        <v>0.88</v>
       </c>
       <c r="D22">
-        <v>0.6</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="B23">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="C23">
-        <v>4.28</v>
+        <v>0.76</v>
       </c>
       <c r="D23">
-        <v>0.55000000000000004</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="B24">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="C24">
-        <v>4.21</v>
+        <v>0.76</v>
       </c>
       <c r="D24">
-        <v>0.56000000000000005</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="B25">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="C25">
-        <v>4.21</v>
+        <v>0.77</v>
       </c>
       <c r="D25">
-        <v>0.56999999999999995</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="B26">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="C26">
-        <v>6.45</v>
+        <v>0.9</v>
       </c>
       <c r="D26">
-        <v>0.56000000000000005</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="B27">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="C27">
-        <v>6.45</v>
+        <v>0.9</v>
       </c>
       <c r="D27">
-        <v>0.55000000000000004</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
+        <v>0.1</v>
+      </c>
+      <c r="B28">
+        <v>1.46</v>
+      </c>
+      <c r="C28">
+        <v>0.9</v>
+      </c>
+      <c r="D28">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>0.15</v>
+      </c>
+      <c r="B29">
+        <v>1.62</v>
+      </c>
+      <c r="C29">
+        <v>0.88</v>
+      </c>
+      <c r="D29">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>0.15</v>
+      </c>
+      <c r="B30">
+        <v>1.64</v>
+      </c>
+      <c r="C30">
+        <v>0.88</v>
+      </c>
+      <c r="D30">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>0.15</v>
+      </c>
+      <c r="B31">
+        <v>1.62</v>
+      </c>
+      <c r="C31">
+        <v>0.86</v>
+      </c>
+      <c r="D31">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>0.25</v>
+      </c>
+      <c r="B32">
+        <v>1.62</v>
+      </c>
+      <c r="C32">
+        <v>0.98</v>
+      </c>
+      <c r="D32">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>0.25</v>
+      </c>
+      <c r="B33">
+        <v>1.62</v>
+      </c>
+      <c r="C33">
+        <v>0.95</v>
+      </c>
+      <c r="D33">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>0.25</v>
+      </c>
+      <c r="B34">
+        <v>1.63</v>
+      </c>
+      <c r="C34">
+        <v>0.94</v>
+      </c>
+      <c r="D34">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>0.5</v>
+      </c>
+      <c r="B35">
+        <v>1.47</v>
+      </c>
+      <c r="C35">
+        <v>1.29</v>
+      </c>
+      <c r="D35">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>0.5</v>
+      </c>
+      <c r="B36">
+        <v>1.48</v>
+      </c>
+      <c r="C36">
+        <v>1.28</v>
+      </c>
+      <c r="D36">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>0.5</v>
+      </c>
+      <c r="B37">
+        <v>1.47</v>
+      </c>
+      <c r="C37">
+        <v>1.3</v>
+      </c>
+      <c r="D37">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>1</v>
+      </c>
+      <c r="B38">
+        <v>1.48</v>
+      </c>
+      <c r="C38">
+        <v>2.02</v>
+      </c>
+      <c r="D38">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>1</v>
+      </c>
+      <c r="B39">
+        <v>1.48</v>
+      </c>
+      <c r="C39">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="D39">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>1</v>
+      </c>
+      <c r="B40">
+        <v>1.49</v>
+      </c>
+      <c r="C40">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="D40">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>1.5</v>
+      </c>
+      <c r="B41">
+        <v>1.55</v>
+      </c>
+      <c r="C41">
+        <v>2.71</v>
+      </c>
+      <c r="D41">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>1.5</v>
+      </c>
+      <c r="B42">
+        <v>1.52</v>
+      </c>
+      <c r="C42">
+        <v>2.69</v>
+      </c>
+      <c r="D42">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>1.5</v>
+      </c>
+      <c r="B43">
+        <v>1.5</v>
+      </c>
+      <c r="C43">
+        <v>2.68</v>
+      </c>
+      <c r="D43">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>2</v>
+      </c>
+      <c r="B44">
+        <v>1.49</v>
+      </c>
+      <c r="C44">
+        <v>3.51</v>
+      </c>
+      <c r="D44">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>2</v>
+      </c>
+      <c r="B45">
+        <v>1.49</v>
+      </c>
+      <c r="C45">
+        <v>3.5</v>
+      </c>
+      <c r="D45">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>2</v>
+      </c>
+      <c r="B46">
+        <v>1.48</v>
+      </c>
+      <c r="C46">
+        <v>3.53</v>
+      </c>
+      <c r="D46">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>2.5</v>
+      </c>
+      <c r="B47">
+        <v>1.44</v>
+      </c>
+      <c r="C47">
+        <v>3.55</v>
+      </c>
+      <c r="D47">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>2.5</v>
+      </c>
+      <c r="B48">
+        <v>1.42</v>
+      </c>
+      <c r="C48">
+        <v>3.63</v>
+      </c>
+      <c r="D48">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>2.5</v>
+      </c>
+      <c r="B49">
+        <v>1.44</v>
+      </c>
+      <c r="C49">
+        <v>3.61</v>
+      </c>
+      <c r="D49">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>3</v>
+      </c>
+      <c r="B50">
+        <v>1.43</v>
+      </c>
+      <c r="C50">
+        <v>4.28</v>
+      </c>
+      <c r="D50">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>3</v>
+      </c>
+      <c r="B51">
+        <v>1.44</v>
+      </c>
+      <c r="C51">
+        <v>4.21</v>
+      </c>
+      <c r="D51">
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>3</v>
+      </c>
+      <c r="B52">
+        <v>1.43</v>
+      </c>
+      <c r="C52">
+        <v>4.21</v>
+      </c>
+      <c r="D52">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53">
         <v>5</v>
       </c>
-      <c r="B28">
+      <c r="B53">
+        <v>1.43</v>
+      </c>
+      <c r="C53">
+        <v>6.45</v>
+      </c>
+      <c r="D53">
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>5</v>
+      </c>
+      <c r="B54">
         <v>1.44</v>
       </c>
-      <c r="C28">
+      <c r="C54">
+        <v>6.45</v>
+      </c>
+      <c r="D54">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>5</v>
+      </c>
+      <c r="B55">
+        <v>1.44</v>
+      </c>
+      <c r="C55">
         <v>6.55</v>
       </c>
-      <c r="D28">
+      <c r="D55">
         <v>0.55000000000000004</v>
       </c>
     </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>7</v>
+      </c>
+      <c r="B56">
+        <v>1.51</v>
+      </c>
+      <c r="C56">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="D56">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>7</v>
+      </c>
+      <c r="B57">
+        <v>1.5</v>
+      </c>
+      <c r="C57">
+        <v>9.86</v>
+      </c>
+      <c r="D57">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>7</v>
+      </c>
+      <c r="B58">
+        <v>1.53</v>
+      </c>
+      <c r="C58">
+        <v>9.76</v>
+      </c>
+      <c r="D58">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>10</v>
+      </c>
+      <c r="B59">
+        <v>1.48</v>
+      </c>
+      <c r="C59">
+        <v>13.18</v>
+      </c>
+      <c r="D59">
+        <v>0.51</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D59">
+    <sortCondition ref="A2:A59"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>